--- a/P3_Feedback_responses.xlsx
+++ b/P3_Feedback_responses.xlsx
@@ -384,10 +384,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -395,10 +395,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -406,10 +406,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -417,10 +417,10 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -428,7 +428,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -439,7 +439,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -450,10 +450,10 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -461,10 +461,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -472,7 +472,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -483,7 +483,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -494,10 +494,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -505,10 +505,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -516,10 +516,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -527,10 +527,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -538,7 +538,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -549,10 +549,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -560,10 +560,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -571,7 +571,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -582,10 +582,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -593,10 +593,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -604,10 +604,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -615,10 +615,10 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -626,7 +626,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>4</v>
@@ -637,10 +637,10 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -659,7 +659,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -670,10 +670,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -681,10 +681,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -692,10 +692,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -703,10 +703,10 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -714,10 +714,10 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -725,10 +725,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -736,10 +736,10 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -747,10 +747,10 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -758,10 +758,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -769,10 +769,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -783,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -791,10 +791,10 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -802,10 +802,10 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -813,10 +813,10 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -824,7 +824,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -838,7 +838,7 @@
         <v>6</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -846,10 +846,10 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -857,10 +857,10 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -871,7 +871,7 @@
         <v>5</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -882,7 +882,7 @@
         <v>7</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -890,10 +890,10 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -901,7 +901,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -912,10 +912,10 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -926,7 +926,7 @@
         <v>5</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
